--- a/ig/DM-JANVIER-2025/alignement-nuva-cipucd.xlsx
+++ b/ig/DM-JANVIER-2025/alignement-nuva-cipucd.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="962">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.818</t>
+    <t>1.0.825</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05</t>
+    <t>2025-01-06</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -891,6 +891,18 @@
     <t>MENCEVAX INJ FL+SRG 1</t>
   </si>
   <si>
+    <t>VAC0620</t>
+  </si>
+  <si>
+    <t>IXCHIQ</t>
+  </si>
+  <si>
+    <t>3400930296448</t>
+  </si>
+  <si>
+    <t>IXCHIQ INJ FL+SRG0,5ML 1</t>
+  </si>
+  <si>
     <t>VAC0050</t>
   </si>
   <si>
@@ -942,7 +954,7 @@
     <t>3400930067727</t>
   </si>
   <si>
-    <t>VAXIGRIPTETRA INJ S0,5ML A/A 1</t>
+    <t>VAXIGRIPTETRA S0,5ML A/AA 1</t>
   </si>
   <si>
     <t>VAC0523</t>
@@ -3148,7 +3160,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E298"/>
+  <dimension ref="A1:E299"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4581,27 +4593,27 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>34</v>
@@ -4632,44 +4644,44 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>34</v>
@@ -4717,27 +4729,27 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>34</v>
@@ -4751,61 +4763,61 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>34</v>
@@ -4836,27 +4848,27 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>34</v>
@@ -4870,27 +4882,27 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>34</v>
@@ -4904,61 +4916,61 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>34</v>
@@ -4972,27 +4984,27 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>34</v>
@@ -5006,61 +5018,61 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>34</v>
@@ -5074,44 +5086,44 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>34</v>
@@ -5193,27 +5205,27 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>34</v>
@@ -5227,61 +5239,61 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C124" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C126" t="s" s="2">
         <v>34</v>
@@ -5295,27 +5307,27 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C127" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C128" t="s" s="2">
         <v>34</v>
@@ -5329,27 +5341,27 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>34</v>
@@ -5397,27 +5409,27 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C133" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C134" t="s" s="2">
         <v>34</v>
@@ -5448,44 +5460,44 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C136" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D137" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C138" t="s" s="2">
         <v>34</v>
@@ -5550,27 +5562,27 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C142" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E142" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C143" t="s" s="2">
         <v>34</v>
@@ -5584,27 +5596,27 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C144" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D144" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>34</v>
@@ -5618,27 +5630,27 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C146" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E146" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>34</v>
@@ -5669,27 +5681,27 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C150" t="s" s="2">
         <v>34</v>
@@ -5720,27 +5732,27 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D152" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E152" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C153" t="s" s="2">
         <v>34</v>
@@ -5839,27 +5851,27 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D159" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C160" t="s" s="2">
         <v>34</v>
@@ -5890,27 +5902,27 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C162" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>34</v>
@@ -5941,27 +5953,27 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C165" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C166" t="s" s="2">
         <v>34</v>
@@ -5992,27 +6004,27 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C168" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D168" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E168" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>34</v>
@@ -6026,44 +6038,44 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C170" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D170" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E170" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C171" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D171" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E171" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>34</v>
@@ -6077,44 +6089,44 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D173" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E173" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C174" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D174" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E174" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C175" t="s" s="2">
         <v>34</v>
@@ -6162,27 +6174,27 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C178" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E178" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>34</v>
@@ -6230,27 +6242,27 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C182" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C183" t="s" s="2">
         <v>34</v>
@@ -6264,27 +6276,27 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C184" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C185" t="s" s="2">
         <v>34</v>
@@ -6315,27 +6327,27 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C187" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C188" t="s" s="2">
         <v>34</v>
@@ -6366,27 +6378,27 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C190" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D190" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E190" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C191" t="s" s="2">
         <v>34</v>
@@ -6485,44 +6497,44 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C197" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D197" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E197" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C198" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D198" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E198" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C199" t="s" s="2">
         <v>34</v>
@@ -6536,27 +6548,27 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C200" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E200" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C201" t="s" s="2">
         <v>34</v>
@@ -6570,44 +6582,44 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C202" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D202" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E202" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C203" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D203" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E203" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C204" t="s" s="2">
         <v>34</v>
@@ -6621,27 +6633,27 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C205" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D205" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E205" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C206" t="s" s="2">
         <v>34</v>
@@ -6655,78 +6667,78 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C207" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D207" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E207" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C208" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D208" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E208" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C209" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D209" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E209" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C210" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D210" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E210" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="C211" t="s" s="2">
         <v>34</v>
@@ -6757,27 +6769,27 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C213" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D213" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E213" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C214" t="s" s="2">
         <v>34</v>
@@ -6808,44 +6820,44 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C216" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D216" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E216" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C217" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D217" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E217" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C218" t="s" s="2">
         <v>34</v>
@@ -6910,44 +6922,44 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C222" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D222" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E222" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C223" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D223" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E223" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C224" t="s" s="2">
         <v>34</v>
@@ -6961,44 +6973,44 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C225" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D225" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E225" t="s" s="2">
-        <v>718</v>
+        <v>738</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C226" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D226" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E226" t="s" s="2">
-        <v>737</v>
+        <v>722</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C227" t="s" s="2">
         <v>34</v>
@@ -7063,27 +7075,27 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="C231" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D231" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E231" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C232" t="s" s="2">
         <v>34</v>
@@ -7114,27 +7126,27 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C234" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D234" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E234" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C235" t="s" s="2">
         <v>34</v>
@@ -7216,61 +7228,61 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C240" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D240" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="E240" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C241" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D241" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E241" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C242" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D242" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E242" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="C243" t="s" s="2">
         <v>34</v>
@@ -7284,44 +7296,44 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C244" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D244" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="E244" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C245" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D245" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="E245" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="C246" t="s" s="2">
         <v>34</v>
@@ -7352,27 +7364,27 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C248" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D248" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="E248" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C249" t="s" s="2">
         <v>34</v>
@@ -7403,27 +7415,27 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C251" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D251" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E251" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C252" t="s" s="2">
         <v>34</v>
@@ -7437,27 +7449,27 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C253" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D253" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="E253" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C254" t="s" s="2">
         <v>34</v>
@@ -7488,27 +7500,27 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C256" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D256" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="E256" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C257" t="s" s="2">
         <v>34</v>
@@ -7539,44 +7551,44 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C259" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D259" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E259" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C260" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D260" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E260" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C261" t="s" s="2">
         <v>34</v>
@@ -7590,44 +7602,44 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C262" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D262" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E262" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C263" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D263" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="E263" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C264" t="s" s="2">
         <v>34</v>
@@ -7658,27 +7670,27 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C266" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D266" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="E266" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C267" t="s" s="2">
         <v>34</v>
@@ -7692,27 +7704,27 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C268" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D268" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="E268" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C269" t="s" s="2">
         <v>34</v>
@@ -7726,27 +7738,27 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C270" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D270" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="E270" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C271" t="s" s="2">
         <v>34</v>
@@ -7760,27 +7772,27 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C272" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D272" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="E272" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C273" t="s" s="2">
         <v>34</v>
@@ -7794,44 +7806,44 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C274" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D274" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="E274" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C275" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D275" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="E275" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="C276" t="s" s="2">
         <v>34</v>
@@ -7879,27 +7891,27 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C279" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D279" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="E279" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C280" t="s" s="2">
         <v>34</v>
@@ -7930,27 +7942,27 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="C282" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D282" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="E282" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C283" t="s" s="2">
         <v>34</v>
@@ -7998,129 +8010,129 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C286" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D286" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="E286" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C287" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D287" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E287" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C288" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D288" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="E288" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C289" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D289" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E289" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C290" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D290" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="E290" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C291" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D291" t="s" s="2">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="E291" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C292" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D292" t="s" s="2">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="E292" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>942</v>
+        <v>928</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>943</v>
+        <v>929</v>
       </c>
       <c r="C293" t="s" s="2">
         <v>34</v>
@@ -8134,78 +8146,78 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C294" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D294" t="s" s="2">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="E294" t="s" s="2">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C295" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D295" t="s" s="2">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="E295" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C296" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D296" t="s" s="2">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="E296" t="s" s="2">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C297" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D297" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="E297" t="s" s="2">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="C298" t="s" s="2">
         <v>34</v>
@@ -8215,6 +8227,23 @@
       </c>
       <c r="E298" t="s" s="2">
         <v>957</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="2">
+        <v>958</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="C299" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D299" t="s" s="2">
+        <v>960</v>
+      </c>
+      <c r="E299" t="s" s="2">
+        <v>961</v>
       </c>
     </row>
   </sheetData>
